--- a/processo_2/synthetic_proposals/PROPOSTA_010/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_010/ficha_pontuacao.xlsx
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,7 +804,11 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4183-9422</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -817,7 +821,11 @@
           <t>Revista Científica Avançada 2</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9308-3430</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -830,7 +838,11 @@
           <t>Revista Científica Avançada 3</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6466-1787</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -929,13 +941,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -971,17 +983,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
@@ -994,7 +1006,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1044,13 +1056,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1063,7 +1075,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1088,7 +1100,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
@@ -1131,7 +1143,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1154,7 +1166,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1200,7 +1212,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1223,7 +1235,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1246,7 +1258,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1269,7 +1281,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1292,7 +1304,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1315,7 +1327,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1338,7 +1350,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1405,13 +1417,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1451,13 +1463,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
@@ -1497,13 +1509,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
@@ -1520,13 +1532,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="G52" t="inlineStr"/>
     </row>
@@ -1556,7 +1568,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1579,7 +1591,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1606,13 +1618,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1625,7 +1637,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1648,7 +1660,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1673,7 +1685,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
@@ -1720,13 +1732,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
@@ -1766,13 +1778,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -1812,13 +1824,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -1856,7 +1868,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
@@ -1871,7 +1883,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
